--- a/data/modelling/atribucion/df_value_sent.xlsx
+++ b/data/modelling/atribucion/df_value_sent.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D256"/>
+  <dimension ref="A1:D232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53049</v>
+        <v>49763.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.06104095291237735</v>
+        <v>0.06945449514858842</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +466,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>265.5</v>
+        <v>300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06277167407530221</v>
+        <v>0.06548716012889735</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7321.5</v>
+        <v>8512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02848748354864208</v>
+        <v>0.03211846401531125</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41899</v>
+        <v>63524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.06077274033682575</v>
+        <v>0.06265009631532437</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66949</v>
+        <v>96999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05287308340857226</v>
+        <v>0.02990712113601339</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80960.5</v>
+        <v>29399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0299095417811527</v>
+        <v>0.08001744090821959</v>
       </c>
     </row>
     <row r="8">
@@ -546,7 +546,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101432</v>
+        <v>139999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01637202397562628</v>
+        <v>0.008769720914989388</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>32999</v>
+        <v>77520.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06509801126298022</v>
+        <v>0.03268268452258141</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>146449</v>
+        <v>38849</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.00904595314807103</v>
+        <v>0.0694963048537533</v>
       </c>
     </row>
     <row r="11">
@@ -594,7 +594,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17050.5</v>
+        <v>13534</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.04162895102507862</v>
+        <v>0.04310862701932793</v>
       </c>
     </row>
     <row r="12">
@@ -610,7 +610,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>339999</v>
+        <v>336999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.005586610106376644</v>
+        <v>-0.001679841616743122</v>
       </c>
     </row>
     <row r="13">
@@ -626,7 +626,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04483946844291023</v>
+        <v>0.05159854728853416</v>
       </c>
     </row>
     <row r="14">
@@ -642,7 +642,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4299.5</v>
+        <v>5587.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.02671616044720156</v>
+        <v>0.03996312652942056</v>
       </c>
     </row>
     <row r="15">
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11498.5</v>
+        <v>20599</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.03615805858458983</v>
+        <v>0.07400817596311639</v>
       </c>
     </row>
     <row r="16">
@@ -674,7 +674,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>23899</v>
+        <v>664.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06778792744551089</v>
+        <v>0.05536665010556017</v>
       </c>
     </row>
     <row r="17">
@@ -690,7 +690,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>612</v>
+        <v>2979.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05372632566707966</v>
+        <v>0.01579604676448852</v>
       </c>
     </row>
     <row r="18">
@@ -706,7 +706,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1930</v>
+        <v>1350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -714,23 +714,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01395540378196029</v>
+        <v>0.03694836818512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
-        <v>1141.5</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Xiaomi</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>precio</t>
+          <t>Marca</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.03189723040730669</v>
+        <v>0.04657841832646629</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +741,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Quantum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -748,7 +750,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.59111099780224</v>
+        <v>0.001995823527153083</v>
       </c>
     </row>
     <row r="21">
@@ -757,7 +759,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quantum</t>
+          <t>Philco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -766,7 +768,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.1072469006654381</v>
+        <v>-0.00851458923808019</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +777,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Philco</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -784,7 +786,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.01222318419067881</v>
+        <v>0.02744658226040246</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +795,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -802,7 +804,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.5437853421013994</v>
+        <v>0.02860702235094749</v>
       </c>
     </row>
     <row r="24">
@@ -811,7 +813,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Kodak</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -820,7 +822,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4372440295411079</v>
+        <v>0.0146478576228134</v>
       </c>
     </row>
     <row r="25">
@@ -829,7 +831,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kodak</t>
+          <t>Alcatel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -838,7 +840,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.3482820311188072</v>
+        <v>0.0345498661516471</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +849,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alcatel</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -856,7 +858,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4912168778201558</v>
+        <v>0.03516127407238032</v>
       </c>
     </row>
     <row r="27">
@@ -865,7 +867,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Sansei</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.454066975026259</v>
+        <v>0.002907417546446919</v>
       </c>
     </row>
     <row r="28">
@@ -883,7 +885,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sansei</t>
+          <t>ZTE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -892,7 +894,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1131213004366082</v>
+        <v>0.003901357997852524</v>
       </c>
     </row>
     <row r="29">
@@ -901,7 +903,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>Energizer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -910,7 +912,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.3456677698878267</v>
+        <v>-0.003129063599244772</v>
       </c>
     </row>
     <row r="30">
@@ -919,7 +921,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Energizer</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +930,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.06944429782942395</v>
+        <v>0.0537249503885462</v>
       </c>
     </row>
     <row r="31">
@@ -937,7 +939,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -946,7 +948,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5892799691716059</v>
+        <v>-0.001978223684956096</v>
       </c>
     </row>
     <row r="32">
@@ -955,7 +957,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>iPro</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -964,7 +966,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.266751785089569</v>
+        <v>0.04206330537709518</v>
       </c>
     </row>
     <row r="33">
@@ -973,7 +975,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -982,7 +984,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.6242466730896322</v>
+        <v>0.0001269929974149508</v>
       </c>
     </row>
     <row r="34">
@@ -991,7 +993,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1000,7 +1002,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.04642983364139006</v>
+        <v>0.06021670595337853</v>
       </c>
     </row>
     <row r="35">
@@ -1009,7 +1011,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1018,7 +1020,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1364465571695314</v>
+        <v>-0.000780235516176613</v>
       </c>
     </row>
     <row r="36">
@@ -1027,7 +1029,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Blackview</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1035,9 +1037,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0.1944145150849813</v>
-      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blackview</t>
+          <t>P&amp;S Mobile</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1053,9 +1053,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.02961895439802525</v>
-      </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1063,7 +1061,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P&amp;S Mobile</t>
+          <t>Ulefone</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1071,9 +1069,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0.03433031668670264</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1081,7 +1077,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ulefone</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1090,7 +1086,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.01543538488364529</v>
+        <v>-3.920760520254528e-05</v>
       </c>
     </row>
     <row r="40">
@@ -1099,7 +1095,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>BLU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1108,7 +1104,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.05910428911975084</v>
+        <v>3.180367159825193e-05</v>
       </c>
     </row>
     <row r="41">
@@ -1117,7 +1113,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BLU</t>
+          <t>RugGear</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1125,9 +1121,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>0.2475085401234764</v>
-      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1135,7 +1129,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RugGear</t>
+          <t>Excess</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1144,7 +1138,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.002616362384243065</v>
+        <v>0.002883111638227907</v>
       </c>
     </row>
     <row r="43">
@@ -1153,7 +1147,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Excess</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1161,9 +1155,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>0.01518538828570305</v>
-      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1171,7 +1163,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Noblex</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1180,7 +1172,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.01513381161991422</v>
+        <v>-0.002851301319938476</v>
       </c>
     </row>
     <row r="45">
@@ -1189,7 +1181,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Noblex</t>
+          <t>Realme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1198,7 +1190,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.09035558212234469</v>
+        <v>0.001655100662014077</v>
       </c>
     </row>
     <row r="46">
@@ -1207,7 +1199,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realme</t>
+          <t>Panacom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1215,7 +1207,9 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>0.001650522852154242</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1223,7 +1217,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Panacom</t>
+          <t>BLU - IPRO - NOKIA - GENERICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1232,7 +1226,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.130022386713451</v>
+        <v>-0.002708177343872018</v>
       </c>
     </row>
     <row r="48">
@@ -1241,7 +1235,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BLU - IPRO - NOKIA - GENERICO</t>
+          <t>T-36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1250,7 +1244,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.02965511026623099</v>
+        <v>0.0003201950758125057</v>
       </c>
     </row>
     <row r="49">
@@ -1259,7 +1253,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T-36</t>
+          <t>BLU,IPRO, OTRAS MARCAS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1267,7 +1261,9 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>0.006268358838355506</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BLU,IPRO, OTRAS MARCAS</t>
+          <t>Asus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1283,9 +1279,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0.02988723689129936</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -1293,7 +1287,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Asus</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1301,7 +1295,9 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0.06951149909121052</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -1309,7 +1305,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>OnePlus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1317,9 +1313,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>0.5531736624194873</v>
-      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -1327,7 +1321,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OnePlus</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1343,7 +1337,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Kanji</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1352,7 +1346,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-0.01517008118166721</v>
+        <v>-0.005707800624412548</v>
       </c>
     </row>
     <row r="55">
@@ -1361,7 +1355,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kanji</t>
+          <t>IPRO - BLU - EXC SEGUN STOCK</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1369,9 +1363,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>0.01814433253851333</v>
-      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1379,7 +1371,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IPRO - BLU - EXC SEGUN STOCK</t>
+          <t>Logic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1387,9 +1379,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D56" t="n">
-        <v>0.06527994098470924</v>
-      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1397,7 +1387,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Logic</t>
+          <t>Doogee</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1406,7 +1396,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.04578944602655192</v>
+        <v>0.0003304756297540774</v>
       </c>
     </row>
     <row r="58">
@@ -1415,7 +1405,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>Infinix</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1423,9 +1413,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>-0.0002243607850996771</v>
-      </c>
+      <c r="D58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1433,7 +1421,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Infinix</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1441,7 +1429,9 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>0.03763850564382664</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1449,7 +1439,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>BlackBerry</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1458,7 +1448,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.4159241206624019</v>
+        <v>0.002605113393061531</v>
       </c>
     </row>
     <row r="61">
@@ -1467,7 +1457,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BlackBerry</t>
+          <t>Cyrus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1475,9 +1465,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D61" t="n">
-        <v>0.1033812245558886</v>
-      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1485,7 +1473,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cyrus</t>
+          <t>Luo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1493,9 +1481,7 @@
           <t>Marca</t>
         </is>
       </c>
-      <c r="D62" t="n">
-        <v>0.0151567023519691</v>
-      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1503,15 +1489,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luo</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marca</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Nombre del sistema operativo</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.03141000120962342</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1519,7 +1507,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>ThreadX</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1528,7 +1516,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.4599232232956729</v>
+        <v>-0.001350248560939864</v>
       </c>
     </row>
     <row r="65">
@@ -1537,7 +1525,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ThreadX</t>
+          <t>iOS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1546,7 +1534,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.002619850338375144</v>
+        <v>0.02525734231726035</v>
       </c>
     </row>
     <row r="66">
@@ -1555,7 +1543,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>S30+</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1563,9 +1551,7 @@
           <t>Nombre del sistema operativo</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>0.1897020886034046</v>
-      </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -1573,7 +1559,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>S30+</t>
+          <t>KaiOS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1581,9 +1567,7 @@
           <t>Nombre del sistema operativo</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>0.002943971437010419</v>
-      </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1591,7 +1575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KaiOS</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1600,7 +1584,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-0.006568608106917435</v>
+        <v>0.007185937177923357</v>
       </c>
     </row>
     <row r="69">
@@ -1609,7 +1593,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Windows Phone</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1618,7 +1602,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.003527598283379443</v>
+        <v>-4.702339957927593e-06</v>
       </c>
     </row>
     <row r="70">
@@ -1627,7 +1611,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Windows Phone</t>
+          <t>KAISTORE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1635,9 +1619,7 @@
           <t>Nombre del sistema operativo</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>0.004588901457197334</v>
-      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1645,7 +1627,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KAISTORE</t>
+          <t>BlackBerry OS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1653,30 +1635,32 @@
           <t>Nombre del sistema operativo</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>0.0009801910251680487</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>BlackBerry OS</t>
-        </is>
+      <c r="B72" t="n">
+        <v>51.92</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nombre del sistema operativo</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Resolución de la cámara trasera principal</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.01877859254133607</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>51.92</v>
+        <v>6.23</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1684,7 +1668,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.01809826811440774</v>
+        <v>0.04218694328525407</v>
       </c>
     </row>
     <row r="74">
@@ -1692,7 +1676,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>6.23</v>
+        <v>2.08</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1700,7 +1684,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.04046178709695353</v>
+        <v>0.003139120897938548</v>
       </c>
     </row>
     <row r="75">
@@ -1708,7 +1692,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>2.08</v>
+        <v>47.77</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1716,7 +1700,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.001257972087840478</v>
+        <v>0.06139084831580115</v>
       </c>
     </row>
     <row r="76">
@@ -1724,7 +1708,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>47.77</v>
+        <v>64.38</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1732,7 +1716,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.05473816523623839</v>
+        <v>0.07083294971931747</v>
       </c>
     </row>
     <row r="77">
@@ -1740,7 +1724,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>64.38</v>
+        <v>105.92</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1748,7 +1732,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.06665027381925646</v>
+        <v>0.03769212267137132</v>
       </c>
     </row>
     <row r="78">
@@ -1756,7 +1740,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>105.92</v>
+        <v>10.39</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1764,7 +1748,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.03164536060756787</v>
+        <v>0.07843391850596468</v>
       </c>
     </row>
     <row r="79">
@@ -1772,7 +1756,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>10.39</v>
+        <v>14.54</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1780,7 +1764,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.07394424222812251</v>
+        <v>0.06014761179723632</v>
       </c>
     </row>
     <row r="80">
@@ -1788,7 +1772,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>14.54</v>
+        <v>27</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1796,7 +1780,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.05523299011140088</v>
+        <v>0.01943982819771398</v>
       </c>
     </row>
     <row r="81">
@@ -1804,7 +1788,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>27</v>
+        <v>31.15</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1812,7 +1796,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.01981216149145033</v>
+        <v>0.01331115238393326</v>
       </c>
     </row>
     <row r="82">
@@ -1820,7 +1804,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>31.15</v>
+        <v>18.7</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1828,7 +1812,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.01158171809983439</v>
+        <v>0.004763630922931164</v>
       </c>
     </row>
     <row r="83">
@@ -1836,7 +1820,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>18.7</v>
+        <v>22.84</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1844,7 +1828,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.004155310138117672</v>
+        <v>0.01912637496353441</v>
       </c>
     </row>
     <row r="84">
@@ -1852,7 +1836,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>22.84</v>
+        <v>39.46</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1860,23 +1844,25 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.01799309026359524</v>
+        <v>0.0004707822966536085</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
-      <c r="B85" t="n">
-        <v>39.46</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1920 px x 1080 px</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Resolución de la cámara trasera principal</t>
+          <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.000437791848592102</v>
+        <v>0.4849369717052777</v>
       </c>
     </row>
     <row r="86">
@@ -1885,7 +1871,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1920 px x 1080 px</t>
+          <t>3840 px x 2160 px</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1894,7 +1880,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.4470678412125768</v>
+        <v>0.662840614298662</v>
       </c>
     </row>
     <row r="87">
@@ -1903,7 +1889,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3840 px x 2160 px</t>
+          <t>7680 px x 4320 px</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1912,7 +1898,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.6233191404758335</v>
+        <v>0.4841795907896512</v>
       </c>
     </row>
     <row r="88">
@@ -1921,7 +1907,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7680 px x 4320 px</t>
+          <t>320 px x 240 px</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1930,7 +1916,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.4283684559003603</v>
+        <v>0.009404652350604729</v>
       </c>
     </row>
     <row r="89">
@@ -1939,7 +1925,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>320 px x 240 px</t>
+          <t>2160 px x 3840 px</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1948,7 +1934,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>-0.006637439612480469</v>
+        <v>0.02222552166933949</v>
       </c>
     </row>
     <row r="90">
@@ -1957,7 +1943,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2160 px x 3840 px</t>
+          <t>1080p a 30/60/240fps</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1965,9 +1951,7 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>0.02163990670653467</v>
-      </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -1975,7 +1959,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1080p a 30/60/240fps</t>
+          <t>3840 x 2160</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -1983,7 +1967,9 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>0.08576374916197992</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -1991,7 +1977,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3840 x 2160</t>
+          <t>1280 px x 720 px</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2000,7 +1986,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.09067192503198994</v>
+        <v>0.1759689375626484</v>
       </c>
     </row>
     <row r="93">
@@ -2009,7 +1995,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1280 px x 720 px</t>
+          <t>8K/24fps, 4K/30/60fps, 1080p/30/60/240/960fps, gyro-EIS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2018,7 +2004,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.1863408922708606</v>
+        <v>0.04862167077574799</v>
       </c>
     </row>
     <row r="94">
@@ -2027,7 +2013,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8K/24fps, 4K/30/60fps, 1080p/30/60/240/960fps, gyro-EIS</t>
+          <t>2048 px x 1152 px</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2036,7 +2022,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.04210298264096628</v>
+        <v>0.0221655835129229</v>
       </c>
     </row>
     <row r="95">
@@ -2045,7 +2031,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2048 px x 1152 px</t>
+          <t>1080 px x 1920 px</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2054,7 +2040,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.02157886720239508</v>
+        <v>0.04334843227986944</v>
       </c>
     </row>
     <row r="96">
@@ -2063,7 +2049,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1080 px x 1920 px</t>
+          <t>1080P@30FPS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2072,7 +2058,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.03866569549498792</v>
+        <v>0.04456556869654454</v>
       </c>
     </row>
     <row r="97">
@@ -2081,7 +2067,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1080P@30FPS</t>
+          <t>1920 x 1080</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2089,9 +2075,7 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>0.053601939553216</v>
-      </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -2099,7 +2083,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1920 x 1080</t>
+          <t>3840 px x 2460 px</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2115,7 +2099,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3840 px x 2460 px</t>
+          <t>3840 px - 2160 px</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2123,7 +2107,9 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>0.04746010963648165</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -2131,7 +2117,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3840 px - 2160 px</t>
+          <t>640 px x 480 px</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2140,7 +2126,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.03202999617774484</v>
+        <v>0.00739138585355604</v>
       </c>
     </row>
     <row r="101">
@@ -2149,7 +2135,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>640 px x 480 px</t>
+          <t>176 px x 144 px</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2157,9 +2143,7 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>0.007196851624893481</v>
-      </c>
+      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -2167,7 +2151,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>176 px x 144 px</t>
+          <t>2048 px x 1080 px</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2183,7 +2167,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2048 px x 1080 px</t>
+          <t>5312 px x 2988 px</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2199,7 +2183,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5312 px x 2988 px</t>
+          <t>3840 px x 1080 px</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2215,7 +2199,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3840 px x 1080 px</t>
+          <t>1440 px x 2960 px</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2231,7 +2215,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1440 px x 2960 px</t>
+          <t>1920 px - 1080 px</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2247,7 +2231,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1920 px - 1080 px</t>
+          <t>480 px x 800 px</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2255,48 +2239,48 @@
           <t>Resolución de video de la cámara trasera</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>-0.007405700595530447</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>480 px x 800 px</t>
-        </is>
+      <c r="B108" t="n">
+        <v>8</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Resolución de video de la cámara trasera</t>
+          <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>-0.007210007726971276</v>
+        <v>0.5171397855191167</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2560 px x 1440 px</t>
-        </is>
+      <c r="B109" t="n">
+        <v>13</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Resolución de video de la cámara trasera</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Resolución de la cámara frontal principal</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.5393861600295818</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2304,7 +2288,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.4710573433048709</v>
+        <v>0.6749467205440955</v>
       </c>
     </row>
     <row r="111">
@@ -2312,7 +2296,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2320,7 +2304,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.5059849997228435</v>
+        <v>0.5477311132515823</v>
       </c>
     </row>
     <row r="112">
@@ -2328,7 +2312,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2336,7 +2320,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.6410749623774608</v>
+        <v>0.466271710686517</v>
       </c>
     </row>
     <row r="113">
@@ -2344,7 +2328,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2352,7 +2336,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.501806735198273</v>
+        <v>0.4199295104193049</v>
       </c>
     </row>
     <row r="114">
@@ -2360,7 +2344,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2368,7 +2352,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.4315114224510055</v>
+        <v>0.1079939184697757</v>
       </c>
     </row>
     <row r="115">
@@ -2376,7 +2360,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2384,7 +2368,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.4108513473610223</v>
+        <v>0.6444861942241141</v>
       </c>
     </row>
     <row r="116">
@@ -2392,7 +2376,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2400,7 +2384,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.08874185350097991</v>
+        <v>2.09579063369117e-06</v>
       </c>
     </row>
     <row r="117">
@@ -2408,7 +2392,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2416,7 +2400,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.6002784086194705</v>
+        <v>0.2070691400371939</v>
       </c>
     </row>
     <row r="118">
@@ -2424,7 +2408,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2432,7 +2416,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.0558287959199019</v>
+        <v>0.1811598701802221</v>
       </c>
     </row>
     <row r="119">
@@ -2440,23 +2424,21 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.08</v>
+        <v>11.1</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="D119" t="n">
-        <v>0.002157366950720936</v>
-      </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2464,7 +2446,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.2050642540731888</v>
+        <v>0.0708730155170476</v>
       </c>
     </row>
     <row r="121">
@@ -2472,23 +2454,21 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>0.1738798653930772</v>
-      </c>
+      <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>11.1</v>
+        <v>24</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2502,7 +2482,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.3</v>
+        <v>25</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2510,7 +2490,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.06191150045757097</v>
+        <v>0.2596937167995327</v>
       </c>
     </row>
     <row r="124">
@@ -2518,43 +2498,47 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0.09624197832986077</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>24</v>
+        <v>1.3</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
           <t>Resolución de la cámara frontal principal</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>0.03997378049721913</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Resolución de la cámara frontal principal</t>
+          <t>Cantidad de cámaras traseras</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.2576936880716241</v>
+        <v>0.4794138148661378</v>
       </c>
     </row>
     <row r="127">
@@ -2562,15 +2546,15 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Resolución de la cámara frontal principal</t>
+          <t>Cantidad de cámaras traseras</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.09439669199809962</v>
+        <v>0.5645251709814393</v>
       </c>
     </row>
     <row r="128">
@@ -2578,15 +2562,15 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Resolución de la cámara frontal principal</t>
+          <t>Cantidad de cámaras traseras</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.04456252448108401</v>
+        <v>0.5757888202270607</v>
       </c>
     </row>
     <row r="129">
@@ -2594,15 +2578,15 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Con cámara</t>
+          <t>Cantidad de cámaras traseras</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.5087412738909717</v>
+        <v>0.3392439294948617</v>
       </c>
     </row>
     <row r="130">
@@ -2610,15 +2594,15 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Con cámara</t>
+          <t>Con lector de huella digital</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-4.617212994941086e-05</v>
+        <v>0.1958911467167834</v>
       </c>
     </row>
     <row r="131">
@@ -2626,15 +2610,15 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cantidad de cámaras traseras</t>
+          <t>Con lector de huella digital</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.4950342312612513</v>
+        <v>0.01501456950888375</v>
       </c>
     </row>
     <row r="132">
@@ -2642,15 +2626,15 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cantidad de cámaras traseras</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.5138795150846103</v>
+        <v>0.05964900744703285</v>
       </c>
     </row>
     <row r="133">
@@ -2658,15 +2642,15 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cantidad de cámaras traseras</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.5278739986144366</v>
+        <v>0.006989622285890072</v>
       </c>
     </row>
     <row r="134">
@@ -2674,15 +2658,15 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cantidad de cámaras traseras</t>
+          <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.3788322039769735</v>
+        <v>0.01721099886431414</v>
       </c>
     </row>
     <row r="135">
@@ -2690,21 +2674,23 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cantidad de cámaras traseras</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>Cantidad de núcleos del procesador</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0.0008264977700230348</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2712,7 +2698,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.5085225177945285</v>
+        <v>0.01343346931339515</v>
       </c>
     </row>
     <row r="137">
@@ -2720,31 +2706,29 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>Cantidad de núcleos del procesador</t>
         </is>
       </c>
-      <c r="D137" t="n">
-        <v>0.02963621332647292</v>
-      </c>
+      <c r="D137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cantidad de núcleos del procesador</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.1979423938638292</v>
+        <v>0.0696397212958151</v>
       </c>
     </row>
     <row r="139">
@@ -2752,15 +2736,15 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cantidad de núcleos del procesador</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.005145668695664941</v>
+        <v>0.06155987325749563</v>
       </c>
     </row>
     <row r="140">
@@ -2768,15 +2752,15 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cantidad de núcleos del procesador</t>
+          <t>Memoria interna</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.09944966879730711</v>
+        <v>-0.01155887058851889</v>
       </c>
     </row>
     <row r="141">
@@ -2784,21 +2768,23 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cantidad de núcleos del procesador</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Memoria interna</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0.066471949835883</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -2806,7 +2792,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.1850568825774105</v>
+        <v>0.06393652211864384</v>
       </c>
     </row>
     <row r="143">
@@ -2814,7 +2800,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -2822,7 +2808,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.1499675472878607</v>
+        <v>0.04410820684859665</v>
       </c>
     </row>
     <row r="144">
@@ -2830,23 +2816,21 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.00390625</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>-0.02075071960962729</v>
-      </c>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>128</v>
+        <v>0.0029296875</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -2854,7 +2838,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.174849694257968</v>
+        <v>4.87450628423806e-05</v>
       </c>
     </row>
     <row r="146">
@@ -2862,7 +2846,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>256</v>
+        <v>0.03125</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2870,7 +2854,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.1487989204446532</v>
+        <v>0.003506159325796313</v>
       </c>
     </row>
     <row r="147">
@@ -2878,7 +2862,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>16</v>
+        <v>0.0078125</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2886,7 +2870,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.1149502401237125</v>
+        <v>0.001180908363929084</v>
       </c>
     </row>
     <row r="148">
@@ -2894,7 +2878,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.00390625</v>
+        <v>4</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2902,7 +2886,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.001863261883854511</v>
+        <v>-0.001924564935150844</v>
       </c>
     </row>
     <row r="149">
@@ -2910,7 +2894,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0029296875</v>
+        <v>512</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2918,7 +2902,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>-0.0008273920600133048</v>
+        <v>0.002615238398446396</v>
       </c>
     </row>
     <row r="150">
@@ -2926,7 +2910,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.03125</v>
+        <v>8</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -2934,7 +2918,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.003743930291506044</v>
+        <v>0.02200564309482555</v>
       </c>
     </row>
     <row r="151">
@@ -2942,39 +2926,35 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.0078125</v>
+        <v>0</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>0.002152220116051619</v>
-      </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>-0.01110254877581231</v>
-      </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>512</v>
+        <v>0.0234375</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2982,7 +2962,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.01594232515208787</v>
+        <v>-0.0002512745943191108</v>
       </c>
     </row>
     <row r="154">
@@ -2990,7 +2970,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>8</v>
+        <v>0.125</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2998,7 +2978,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.05288236449258287</v>
+        <v>1.310185067480457e-05</v>
       </c>
     </row>
     <row r="155">
@@ -3006,7 +2986,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>0.0009765625</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3020,7 +3000,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>6</v>
+        <v>0.048828125</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3034,7 +3014,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0234375</v>
+        <v>0.015625</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3048,37 +3028,37 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="D158" t="n">
-        <v>-0.001626379937753536</v>
-      </c>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0009765625</v>
+        <v>2</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
           <t>Memoria interna</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>-0.001094714658623178</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>0.048828125</v>
+        <v>1</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3092,29 +3072,31 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0.015625</v>
+        <v>4</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0.0636718742058959</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
+          <t>Memoria RAM</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.002413644559185928</v>
+        <v>0.03809040844438784</v>
       </c>
     </row>
     <row r="163">
@@ -3122,35 +3104,39 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>-0.006744141055658535</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Memoria interna</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Memoria RAM</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0.07555889758232634</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3158,7 +3144,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.1624401378040164</v>
+        <v>0.06920483248138894</v>
       </c>
     </row>
     <row r="166">
@@ -3166,7 +3152,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3174,7 +3160,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.05955423899256177</v>
+        <v>0.04176226375208278</v>
       </c>
     </row>
     <row r="167">
@@ -3182,7 +3168,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0.25</v>
+        <v>12</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3190,7 +3176,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>-0.01437891471327345</v>
+        <v>0.03733570751036371</v>
       </c>
     </row>
     <row r="168">
@@ -3198,7 +3184,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3206,7 +3192,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.2023762448719454</v>
+        <v>0.07191378028700354</v>
       </c>
     </row>
     <row r="169">
@@ -3214,7 +3200,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>8</v>
+        <v>0.00390625</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3222,7 +3208,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.2030845159189585</v>
+        <v>4.279885593957771e-05</v>
       </c>
     </row>
     <row r="170">
@@ -3230,7 +3216,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>0.03125</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3238,7 +3224,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.1074892744216801</v>
+        <v>-0.0005639163898592021</v>
       </c>
     </row>
     <row r="171">
@@ -3246,7 +3232,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>12</v>
+        <v>0.0078125</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3254,7 +3240,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.09106423285981979</v>
+        <v>0.001036854278126005</v>
       </c>
     </row>
     <row r="172">
@@ -3262,7 +3248,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3270,7 +3256,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.1901450967544722</v>
+        <v>-0.001113152389813844</v>
       </c>
     </row>
     <row r="173">
@@ -3278,39 +3264,35 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.00390625</v>
+        <v>0.0234375</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
           <t>Memoria RAM</t>
         </is>
       </c>
-      <c r="D173" t="n">
-        <v>0.001000309696869581</v>
-      </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0.03125</v>
+        <v>0</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
           <t>Memoria RAM</t>
         </is>
       </c>
-      <c r="D174" t="n">
-        <v>-0.005519444859260429</v>
-      </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0078125</v>
+        <v>0.0625</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -3318,7 +3300,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.002078337067394134</v>
+        <v>1.150361055818129e-05</v>
       </c>
     </row>
     <row r="176">
@@ -3326,7 +3308,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0.5</v>
+        <v>32</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -3334,7 +3316,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.00368877489254162</v>
+        <v>0.001160352215611092</v>
       </c>
     </row>
     <row r="177">
@@ -3342,7 +3324,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0234375</v>
+        <v>0.0009765625</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3356,7 +3338,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>0.00048828125</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -3370,7 +3352,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0625</v>
+        <v>1.5</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -3378,7 +3360,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.000760238802884467</v>
+        <v>0.01346458321749014</v>
       </c>
     </row>
     <row r="180">
@@ -3386,59 +3368,61 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>32</v>
+        <v>0.125</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
           <t>Memoria RAM</t>
         </is>
       </c>
-      <c r="D180" t="n">
-        <v>0.003923949297812012</v>
-      </c>
+      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0009765625</v>
+        <v>166.54</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>0.03512048386087473</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>0.00048828125</v>
+        <v>137.64</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>0.05610750490066634</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>1.5</v>
+        <v>58.18</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.03371054821273993</v>
+        <v>0.0232194526726603</v>
       </c>
     </row>
     <row r="184">
@@ -3446,15 +3430,15 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>0.125</v>
+        <v>159.32</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
+          <t>Tamaño de la pantalla</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>-0.004441496720291404</v>
+        <v>0.0437332647434833</v>
       </c>
     </row>
     <row r="185">
@@ -3462,35 +3446,39 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>256</v>
+        <v>173.76</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>-0.01168614802723383</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>128</v>
+        <v>144.87</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Memoria RAM</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Tamaño de la pantalla</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>0.0785554228419507</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>166.54</v>
+        <v>152.09</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -3498,7 +3486,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.3308365377839236</v>
+        <v>0.0519498827318091</v>
       </c>
     </row>
     <row r="188">
@@ -3506,7 +3494,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>137.64</v>
+        <v>43.73</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -3514,7 +3502,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.4134241792718403</v>
+        <v>0.01830305500297293</v>
       </c>
     </row>
     <row r="189">
@@ -3522,7 +3510,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>58.18</v>
+        <v>50.96</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -3530,7 +3518,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.07475003553402997</v>
+        <v>0.008303717680479852</v>
       </c>
     </row>
     <row r="190">
@@ -3538,7 +3526,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>159.32</v>
+        <v>123.2</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3546,7 +3534,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.4798753349531289</v>
+        <v>0.05626755612458856</v>
       </c>
     </row>
     <row r="191">
@@ -3554,7 +3542,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>173.76</v>
+        <v>115.97</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3562,7 +3550,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.4052615498953138</v>
+        <v>0.03933857880346662</v>
       </c>
     </row>
     <row r="192">
@@ -3570,7 +3558,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>144.87</v>
+        <v>130.42</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3578,7 +3566,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.3932418694938128</v>
+        <v>0.05152495567522829</v>
       </c>
     </row>
     <row r="193">
@@ -3586,7 +3574,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>152.09</v>
+        <v>36.51</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3594,7 +3582,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.3665712730590657</v>
+        <v>0.01306396649947672</v>
       </c>
     </row>
     <row r="194">
@@ -3602,7 +3590,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>43.73</v>
+        <v>101.52</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3610,7 +3598,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.005060264167952304</v>
+        <v>0.03400562649539231</v>
       </c>
     </row>
     <row r="195">
@@ -3618,7 +3606,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>50.96</v>
+        <v>191.824</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3626,7 +3614,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>-0.0001427918836030434</v>
+        <v>0.001477151406584438</v>
       </c>
     </row>
     <row r="196">
@@ -3634,23 +3622,21 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>123.2</v>
+        <v>72.63</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="D196" t="n">
-        <v>0.2948536589199951</v>
-      </c>
+      <c r="D196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>115.97</v>
+        <v>108.75</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3658,7 +3644,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.0980679971833246</v>
+        <v>0.004577317877027661</v>
       </c>
     </row>
     <row r="198">
@@ -3666,23 +3652,21 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>130.42</v>
+        <v>7.61</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
           <t>Tamaño de la pantalla</t>
         </is>
       </c>
-      <c r="D198" t="n">
-        <v>0.2949650586031046</v>
-      </c>
+      <c r="D198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>36.51</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3690,101 +3674,115 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>-0.008226217543495021</v>
+        <v>0.002201098651721031</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
         <v>198</v>
       </c>
-      <c r="B200" t="n">
-        <v>101.52</v>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Full HD+</t>
+        </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.0004582812329805833</v>
+        <v>0.0522622709583403</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
         <v>199</v>
       </c>
-      <c r="B201" t="n">
-        <v>191.824</v>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>FWVGA+</t>
+        </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.055146061347526</v>
+        <v>0.0002897275536851315</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="B202" t="n">
-        <v>72.63</v>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>HD+</t>
+        </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.0007304574759758387</v>
+        <v>0.03639937257969237</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="B203" t="n">
-        <v>108.75</v>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>FHD+</t>
+        </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>-4.046233916203568e-06</v>
+        <v>0.02723036612554883</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
         <v>202</v>
       </c>
-      <c r="B204" t="n">
-        <v>7.61</v>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Quad HD+</t>
+        </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>0.03440397406521842</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
         <v>203</v>
       </c>
-      <c r="B205" t="n">
-        <v>87.06999999999999</v>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tamaño de la pantalla</t>
+          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>-0.008621871705639383</v>
+        <v>0.01449704343298393</v>
       </c>
     </row>
     <row r="206">
@@ -3793,7 +3791,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Full HD+</t>
+          <t>QQVGA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -3802,7 +3800,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.1502844344678471</v>
+        <v>-0.0009343461008677896</v>
       </c>
     </row>
     <row r="207">
@@ -3811,7 +3809,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FWVGA+</t>
+          <t>QVGA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -3819,9 +3817,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D207" t="n">
-        <v>0.005543611884225948</v>
-      </c>
+      <c r="D207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -3829,7 +3825,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HD+</t>
+          <t>QXGA+</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -3838,7 +3834,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.08681250226514581</v>
+        <v>0.009732526858047836</v>
       </c>
     </row>
     <row r="209">
@@ -3847,7 +3843,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FHD+</t>
+          <t>QHD+</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -3855,9 +3851,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D209" t="n">
-        <v>0.06485246418726791</v>
-      </c>
+      <c r="D209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -3865,7 +3859,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Quad HD+</t>
+          <t>Full HD</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -3873,9 +3867,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D210" t="n">
-        <v>0.09990060537504714</v>
-      </c>
+      <c r="D210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -3883,7 +3875,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>1080 px x 2448 px</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -3891,9 +3883,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D211" t="n">
-        <v>0.04834082181939357</v>
-      </c>
+      <c r="D211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -3901,7 +3891,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>QQVGA</t>
+          <t>FWVGA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -3909,9 +3899,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D212" t="n">
-        <v>-0.00062148169823676</v>
-      </c>
+      <c r="D212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -3919,7 +3907,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>QVGA</t>
+          <t>QHD</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -3935,7 +3923,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>QXGA+</t>
+          <t>WQHD+</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -3943,9 +3931,7 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D214" t="n">
-        <v>0.02785916739711108</v>
-      </c>
+      <c r="D214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -3953,7 +3939,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>QHD+</t>
+          <t>Quad HD</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -3961,688 +3947,280 @@
           <t xml:space="preserve">Tipo de resolución de la pantalla </t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="n">
+        <v>0.00122017403191525</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
         <v>214</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Full HD</t>
-        </is>
+      <c r="B216" t="n">
+        <v>4990</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0.05181911979896497</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
         <v>215</v>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>1080 px x 2448 px</t>
-        </is>
+      <c r="B217" t="n">
+        <v>2530</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0.009121943466153012</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
         <v>216</v>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>FWVGA</t>
-        </is>
+      <c r="B218" t="n">
+        <v>755</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0.0177674234319565</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
         <v>217</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>QHD</t>
-        </is>
+      <c r="B219" t="n">
+        <v>4375</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0.04339392952299431</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
         <v>218</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>WQHD+</t>
-        </is>
+      <c r="B220" t="n">
+        <v>2704</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
+          <t>Capacidad de la batería</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0.004942272705447712</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
         <v>219</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Quad HD</t>
-        </is>
+      <c r="B221" t="n">
+        <v>3650</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo de resolución de la pantalla </t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>-0.0002040645055713354</v>
+        <v>0.01920924341516101</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
         <v>220</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>LCD</t>
-        </is>
+      <c r="B222" t="n">
+        <v>4100</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>-0.0009995699547069397</v>
+        <v>0.05389901829984427</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
         <v>221</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
+      <c r="B223" t="n">
+        <v>1150</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.105142198372397</v>
+        <v>0.0084905878655651</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
         <v>222</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>TFT</t>
-        </is>
+      <c r="B224" t="n">
+        <v>3287</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.06380913588158936</v>
+        <v>0.01455821956785698</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
         <v>223</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
+      <c r="B225" t="n">
+        <v>1985</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.09206792346581703</v>
+        <v>0.0005776819066437616</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
         <v>224</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Super AMOLED</t>
-        </is>
+      <c r="B226" t="n">
+        <v>1512</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.1580690454849484</v>
+        <v>-0.001228834896842937</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>AMOLED</t>
-        </is>
+      <c r="B227" t="n">
+        <v>1782.5</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.1170766472528716</v>
+        <v>0.0006729752080871451</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
         <v>226</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>PLS</t>
-        </is>
+      <c r="B228" t="n">
+        <v>3055</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.06622185902756454</v>
+        <v>0.03093644854645211</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Dynamic AMOLED 2X</t>
-        </is>
+      <c r="B229" t="n">
+        <v>5805</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.09840736673052297</v>
+        <v>0.01373704869535684</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
         <v>228</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Dynamic AMOLED</t>
-        </is>
+      <c r="B230" t="n">
+        <v>4660</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.09909379627500191</v>
+        <v>0.004636630066912889</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>HDR10+</t>
-        </is>
+      <c r="B231" t="n">
+        <v>2856</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
+          <t>Capacidad de la batería</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.009123628319310037</v>
+        <v>0.003930652356011651</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
         <v>230</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>LTPO</t>
-        </is>
+      <c r="B232" t="n">
+        <v>2262.5</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Fluid AMOLED</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="1" t="n">
-        <v>232</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>PLS TFT LCD</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="1" t="n">
-        <v>233</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>LTPS</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>0.04484640205806836</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="1" t="n">
-        <v>234</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>POLED</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>0.03064212450624161</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Optic AMOLED</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Tecnología de la pantalla</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>236</v>
-      </c>
-      <c r="B238" t="n">
-        <v>1</v>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>0.3812551074411039</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>237</v>
-      </c>
-      <c r="B239" t="n">
-        <v>0</v>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Con pantalla táctil</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>0.002091917805954271</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>238</v>
-      </c>
-      <c r="B240" t="n">
-        <v>4990</v>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
           <t>Capacidad de la batería</t>
         </is>
       </c>
-      <c r="D240" t="n">
-        <v>0.04113531253365871</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>239</v>
-      </c>
-      <c r="B241" t="n">
-        <v>2559</v>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>0.006743067216573602</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="B242" t="n">
-        <v>402</v>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>0.01197257086163076</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>241</v>
-      </c>
-      <c r="B243" t="n">
-        <v>4650</v>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>0.03907707511124866</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="B244" t="n">
-        <v>4300</v>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>0.01323103925955814</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>243</v>
-      </c>
-      <c r="B245" t="n">
-        <v>2730.5</v>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>0.002502643228752549</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>244</v>
-      </c>
-      <c r="B246" t="n">
-        <v>3900</v>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>0.03990230857552717</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="B247" t="n">
-        <v>1010</v>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>0.005777763367201471</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>246</v>
-      </c>
-      <c r="B248" t="n">
-        <v>3443.5</v>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>0.02151254830560398</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="1" t="n">
-        <v>247</v>
-      </c>
-      <c r="B249" t="n">
-        <v>1925</v>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>-0.002856473918661407</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="n">
-        <v>248</v>
-      </c>
-      <c r="B250" t="n">
-        <v>1375</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>0.001337593829580783</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="n">
-        <v>249</v>
-      </c>
-      <c r="B251" t="n">
-        <v>1690.5</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>-0.003276172065703579</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="n">
-        <v>250</v>
-      </c>
-      <c r="B252" t="n">
-        <v>3142.5</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>0.005480922581208027</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>251</v>
-      </c>
-      <c r="B253" t="n">
-        <v>5600</v>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>0.009771700067409836</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="B254" t="n">
-        <v>2925</v>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>0.02270830698546485</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="n">
-        <v>253</v>
-      </c>
-      <c r="B255" t="n">
-        <v>8200</v>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>0.0001716630924981419</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="n">
-        <v>254</v>
-      </c>
-      <c r="B256" t="n">
-        <v>2235</v>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Capacidad de la batería</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>0.004361297098789334</v>
+      <c r="D232" t="n">
+        <v>0.005659774823393425</v>
       </c>
     </row>
   </sheetData>
